--- a/DuePrint3 Wire List.xlsx
+++ b/DuePrint3 Wire List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jared\Documents\GitHub\DuePrint3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A371B7-FF35-4A56-B935-D1B3C11EA22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F4AF451-F950-4D98-8880-70332CBBE61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10500" windowWidth="25800" windowHeight="10500" xr2:uid="{3CF24DAB-A4E5-4B0F-806A-3EDA7AAF8571}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="22500" windowHeight="17805" xr2:uid="{3CF24DAB-A4E5-4B0F-806A-3EDA7AAF8571}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2455,7 +2456,7 @@
         <v>170</v>
       </c>
       <c r="F55" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>159</v>
@@ -2481,7 +2482,7 @@
         <v>171</v>
       </c>
       <c r="F56" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>159</v>
@@ -2498,7 +2499,7 @@
         <v>180</v>
       </c>
       <c r="C57" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>229</v>
@@ -2507,7 +2508,7 @@
         <v>172</v>
       </c>
       <c r="F57" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>158</v>
@@ -2524,7 +2525,7 @@
         <v>181</v>
       </c>
       <c r="C58" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>229</v>
@@ -2533,7 +2534,7 @@
         <v>173</v>
       </c>
       <c r="F58" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>158</v>
@@ -2550,7 +2551,7 @@
         <v>182</v>
       </c>
       <c r="C59" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>229</v>
@@ -2559,7 +2560,7 @@
         <v>174</v>
       </c>
       <c r="F59" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>158</v>
@@ -2576,7 +2577,7 @@
         <v>183</v>
       </c>
       <c r="C60" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>229</v>
@@ -2585,7 +2586,7 @@
         <v>175</v>
       </c>
       <c r="F60" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>158</v>
@@ -2611,7 +2612,7 @@
         <v>176</v>
       </c>
       <c r="F61" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>159</v>
@@ -2637,7 +2638,7 @@
         <v>177</v>
       </c>
       <c r="F62" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>159</v>
@@ -2654,7 +2655,7 @@
         <v>184</v>
       </c>
       <c r="C63" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>229</v>
@@ -2663,7 +2664,7 @@
         <v>178</v>
       </c>
       <c r="F63" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>158</v>
@@ -2680,7 +2681,7 @@
         <v>185</v>
       </c>
       <c r="C64" s="1">
-        <v>39000039</v>
+        <v>39000046</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>229</v>
@@ -2689,7 +2690,7 @@
         <v>179</v>
       </c>
       <c r="F64" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>158</v>
@@ -2715,7 +2716,7 @@
         <v>186</v>
       </c>
       <c r="F65" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>168</v>
@@ -2741,7 +2742,7 @@
         <v>187</v>
       </c>
       <c r="F66" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>168</v>
@@ -2767,7 +2768,7 @@
         <v>188</v>
       </c>
       <c r="F67" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>168</v>
@@ -2793,7 +2794,7 @@
         <v>189</v>
       </c>
       <c r="F68" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>168</v>
@@ -2819,7 +2820,7 @@
         <v>190</v>
       </c>
       <c r="F69" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>169</v>
@@ -2845,7 +2846,7 @@
         <v>191</v>
       </c>
       <c r="F70" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>169</v>
@@ -2871,7 +2872,7 @@
         <v>192</v>
       </c>
       <c r="F71" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>169</v>
@@ -2897,7 +2898,7 @@
         <v>193</v>
       </c>
       <c r="F72" s="1">
-        <v>39000041</v>
+        <v>39000048</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>169</v>

--- a/DuePrint3 Wire List.xlsx
+++ b/DuePrint3 Wire List.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jared\Documents\GitHub\DuePrint3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F4AF451-F950-4D98-8880-70332CBBE61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2110C38E-49FB-4C4B-9613-832E6FCF2BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="22500" windowHeight="17805" xr2:uid="{3CF24DAB-A4E5-4B0F-806A-3EDA7AAF8571}"/>
+    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{3CF24DAB-A4E5-4B0F-806A-3EDA7AAF8571}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet1 (2)'!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="284">
   <si>
     <t>From</t>
   </si>
@@ -733,6 +734,165 @@
   </si>
   <si>
     <t>P2 (39012086)</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>INTF</t>
+  </si>
+  <si>
+    <t>J16</t>
+  </si>
+  <si>
+    <t>120V ON</t>
+  </si>
+  <si>
+    <t>48V  RTN PWR</t>
+  </si>
+  <si>
+    <t>MOTOR EN MB</t>
+  </si>
+  <si>
+    <t>48V</t>
+  </si>
+  <si>
+    <t>CHAMBER HEATER ENABLE</t>
+  </si>
+  <si>
+    <t>PRINT HEAD BLOWER ENABLE</t>
+  </si>
+  <si>
+    <t>POWER ON</t>
+  </si>
+  <si>
+    <t>X-AXIS HOME</t>
+  </si>
+  <si>
+    <t>Y-AXIS HOME</t>
+  </si>
+  <si>
+    <t>Z-AXIS HOME</t>
+  </si>
+  <si>
+    <t>POWER I/O</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>EXTRUDER SUPPORT HEATER ENABLE</t>
+  </si>
+  <si>
+    <t>EXTRUDER MODEL HEATER ENABLE</t>
+  </si>
+  <si>
+    <t>DOOR SOLENOID ENABLE</t>
+  </si>
+  <si>
+    <t>CHAMBER TEMP THERM</t>
+  </si>
+  <si>
+    <t>CHAMBER TEMP THERM VSSA0</t>
+  </si>
+  <si>
+    <t>PRINT HEAD SUPP THERM VSSA2</t>
+  </si>
+  <si>
+    <t>PRINT HEAD SUPP THERM</t>
+  </si>
+  <si>
+    <t>PRINT HEAD MODEL THERM</t>
+  </si>
+  <si>
+    <t>PRINT HEAD MODEL THERM VSSA1</t>
+  </si>
+  <si>
+    <t>io0.out</t>
+  </si>
+  <si>
+    <t>out4</t>
+  </si>
+  <si>
+    <t>io1.out</t>
+  </si>
+  <si>
+    <t>io3.out</t>
+  </si>
+  <si>
+    <t>io2.in</t>
+  </si>
+  <si>
+    <t>io4.out</t>
+  </si>
+  <si>
+    <t>io6.in</t>
+  </si>
+  <si>
+    <t>io2.out</t>
+  </si>
+  <si>
+    <t>io4.in</t>
+  </si>
+  <si>
+    <t>io7.out</t>
+  </si>
+  <si>
+    <t>io3.in</t>
+  </si>
+  <si>
+    <t>io5.out</t>
+  </si>
+  <si>
+    <t>io0.in</t>
+  </si>
+  <si>
+    <t>io6.out</t>
+  </si>
+  <si>
+    <t>io1.in</t>
+  </si>
+  <si>
+    <t>temp0</t>
+  </si>
+  <si>
+    <t>io5.in</t>
+  </si>
+  <si>
+    <t>io8.in</t>
+  </si>
+  <si>
+    <t>temp2</t>
+  </si>
+  <si>
+    <t>io7.in</t>
+  </si>
+  <si>
+    <t>temp1</t>
+  </si>
+  <si>
+    <t>SPHD-002T-P0.5</t>
+  </si>
+  <si>
+    <t>(PHDR-30VS)</t>
+  </si>
+  <si>
+    <t>P(61900511621)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>J8</t>
   </si>
 </sst>
 </file>
@@ -1125,15 +1285,1591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F061D89-7440-4290-8736-92859B5FF9A2}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:L55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="21.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f t="shared" ref="E2:E29" si="0">B2&amp;" "&amp;C2&amp;" "&amp;D2</f>
+        <v>INTF J16 2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K2" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K3" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K5" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="1">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K6" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="1">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K8" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K10" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="1">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 12</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K12" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="1">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 14</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K14" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="1">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 15</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K15" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="1">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 16</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K16" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="1">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K17" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D18" s="1">
+        <v>18</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 18</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="K18" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="1">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 19</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K19" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20" s="1">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 20</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K20" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="1">
+        <v>21</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 21</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K21" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" s="1">
+        <v>22</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 22</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K22" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23" s="1">
+        <v>23</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 23</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="1">
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 24</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K24" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="1">
+        <v>26</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 26</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K25" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="1">
+        <v>27</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K26" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="1">
+        <v>28</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 28</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K27" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="1">
+        <v>29</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 29</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="1">
+        <v>30</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INTF J16 30</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I34" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I35" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K35" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K38" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I39" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K39" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K40" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I41" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K41" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I42" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K42" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F43" s="1">
+        <v>39000046</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I43" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K43" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I44" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K44" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I45" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K45" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I46" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K46" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K47" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K48" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I49" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K49" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I50" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K50" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I51" s="1">
+        <v>39000048</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K51" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f t="shared" ref="E52:E55" si="1">B52&amp;" "&amp;C52&amp;" "&amp;D52</f>
+        <v>INTF J3 1</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>INTF J3 2</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>INTF J8 1</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>INTF J8 2</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{4F061D89-7440-4290-8736-92859B5FF9A2}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE15543-C85D-44C4-A848-FFC3ACD5F66C}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="1"/>
@@ -1166,7 +2902,7 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>205</v>
       </c>
@@ -1192,7 +2928,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>205</v>
       </c>
@@ -1218,7 +2954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>205</v>
       </c>
@@ -1244,7 +2980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>205</v>
       </c>
@@ -1270,7 +3006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>205</v>
       </c>
@@ -1296,7 +3032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>205</v>
       </c>
@@ -1322,7 +3058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>205</v>
       </c>
@@ -1348,7 +3084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>205</v>
       </c>
@@ -1374,7 +3110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>205</v>
       </c>
@@ -1400,7 +3136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>205</v>
       </c>
@@ -1426,7 +3162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>205</v>
       </c>
@@ -1452,7 +3188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>205</v>
       </c>
@@ -1478,7 +3214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>205</v>
       </c>
@@ -1504,7 +3240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>205</v>
       </c>
@@ -1530,7 +3266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>205</v>
       </c>
@@ -1556,7 +3292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>205</v>
       </c>
@@ -1582,7 +3318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>205</v>
       </c>
@@ -1608,7 +3344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>199</v>
       </c>
@@ -1634,7 +3370,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>199</v>
       </c>
@@ -1660,7 +3396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>199</v>
       </c>
@@ -1686,7 +3422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>199</v>
       </c>
@@ -1712,7 +3448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>199</v>
       </c>
@@ -1738,7 +3474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>199</v>
       </c>
@@ -1764,7 +3500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>199</v>
       </c>
@@ -1790,7 +3526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>199</v>
       </c>
@@ -1816,7 +3552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>199</v>
       </c>
@@ -1842,7 +3578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>199</v>
       </c>
@@ -1868,7 +3604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>199</v>
       </c>
@@ -1894,7 +3630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>199</v>
       </c>
@@ -1920,7 +3656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>199</v>
       </c>
@@ -1946,7 +3682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>199</v>
       </c>
@@ -1972,7 +3708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>199</v>
       </c>
@@ -1998,7 +3734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>206</v>
       </c>
@@ -2021,7 +3757,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>206</v>
       </c>
@@ -2044,7 +3780,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>206</v>
       </c>
@@ -2067,7 +3803,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>206</v>
       </c>
@@ -2090,7 +3826,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>206</v>
       </c>
@@ -2113,7 +3849,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>206</v>
       </c>
@@ -2136,7 +3872,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>206</v>
       </c>
@@ -2159,7 +3895,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>207</v>
       </c>
@@ -2182,7 +3918,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>207</v>
       </c>
@@ -2233,7 +3969,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>208</v>
       </c>
@@ -2339,7 +4075,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>152</v>
       </c>
@@ -2359,7 +4095,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>152</v>
       </c>
@@ -2907,9 +4643,43 @@
         <v>22</v>
       </c>
     </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F78" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{4F061D89-7440-4290-8736-92859B5FF9A2}"/>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <autoFilter ref="A1:H72" xr:uid="{4F061D89-7440-4290-8736-92859B5FF9A2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CHASSIS"/>
+        <filter val="FREE"/>
+        <filter val="HEAD UMB J9 1"/>
+        <filter val="HEAD UMB J9 10"/>
+        <filter val="HEAD UMB J9 11"/>
+        <filter val="HEAD UMB J9 12"/>
+        <filter val="HEAD UMB J9 16"/>
+        <filter val="HEAD UMB J9 19"/>
+        <filter val="HEAD UMB J9 2"/>
+        <filter val="HEAD UMB J9 3"/>
+        <filter val="HEAD UMB J9 6"/>
+        <filter val="HEAD UMB J9 9"/>
+        <filter val="LIVE"/>
+        <filter val="NEUTRAL"/>
+        <filter val="STRATASYS PDB J13/J14"/>
+        <filter val="STRATASYS PDB J14/J18"/>
+        <filter val="STRATASYS PDB J15/J17"/>
+        <filter val="Y/Z J8 1"/>
+        <filter val="Y/Z J8 2"/>
+        <filter val="Y/Z J8 3"/>
+        <filter val="Y/Z J8 4"/>
+        <filter val="Y/Z J8 5"/>
+        <filter val="Y/Z J8 6"/>
+        <filter val="Y/Z J8 7"/>
+        <filter val="Y/Z J8 8"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
